--- a/data/trans_bre/P6907S1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 12,24</t>
+          <t>-7,59; 13,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 0,0</t>
+          <t>-19,73; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -1,77</t>
+          <t>-16,38; -1,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 5,48</t>
+          <t>-12,74; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 329,61</t>
+          <t>-100,0; 403,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 6,46</t>
+          <t>-6,75; 5,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -2,11</t>
+          <t>-11,97; -2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,58</t>
+          <t>-4,59; 1,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,4</t>
+          <t>-7,91; 2,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 102,6</t>
+          <t>-61,06; 69,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 254,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,22; 37,66</t>
+          <t>-62,4; 41,32</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 15,41</t>
+          <t>-8,32; 16,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,12</t>
+          <t>6,0; 47,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,98</t>
+          <t>-4,3; 8,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 6,75</t>
+          <t>-19,58; 6,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 212,29</t>
+          <t>-50,23; 211,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,97; 70,06</t>
+          <t>-68,94; 68,82</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,84</t>
+          <t>-3,18; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,17</t>
+          <t>-7,54; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,06</t>
+          <t>-3,74; 2,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 1,65</t>
+          <t>-7,33; 1,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 88,33</t>
+          <t>-29,84; 92,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,97</t>
+          <t>-100,0; 124,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,69; 110,02</t>
+          <t>-80,13; 134,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 21,01</t>
+          <t>-56,16; 21,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6907S1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,6</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-45,19%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 13,35</t>
+          <t>-6,24; 14,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 0,0</t>
+          <t>-20,03; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,38; -1,8</t>
+          <t>-15,22; -1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 5,24</t>
+          <t>-8,29; 12,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 403,15</t>
+          <t>-76,86; 461,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-27,02%</t>
+          <t>-12,2%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,3</t>
+          <t>-6,83; 6,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -2,15</t>
+          <t>-12,04; -2,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,57</t>
+          <t>-4,48; 1,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,46</t>
+          <t>-6,24; 3,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 69,29</t>
+          <t>-60,49; 97,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 139,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 41,32</t>
+          <t>-52,97; 54,23</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-28,83%</t>
+          <t>-24,89%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 16,41</t>
+          <t>-9,39; 15,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 47,11</t>
+          <t>5,93; 46,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 8,81</t>
+          <t>-4,3; 9,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 6,57</t>
+          <t>-19,18; 6,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 211,25</t>
+          <t>-52,54; 192,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-68,94; 68,82</t>
+          <t>-71,78; 64,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,07%</t>
+          <t>-10,33%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,98</t>
+          <t>-3,3; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,45</t>
+          <t>-7,32; 2,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,45</t>
+          <t>-3,82; 1,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 1,67</t>
+          <t>-5,81; 3,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 92,78</t>
+          <t>-30,46; 93,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,13</t>
+          <t>-100,0; 136,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 134,17</t>
+          <t>-82,04; 120,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 21,03</t>
+          <t>-44,12; 55,22</t>
         </is>
       </c>
     </row>
